--- a/stories/arbres/ATOM-SEC.MAI.003-02.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Estéban est à la maison. Papa ouvre la porte du balcon. L'air sent le thym. Estéban reste avec l'adulte. Papa dit : on reste derrière la protection. Estéban pose les pieds au sol. Les pieds restent au sol. Il sent le bois sous les chaussettes. La protection est devant lui. Estéban pose les mains sur la protection. Il reste derrière la protection. Un oiseau chante. Estéban dit : papa, l'oiseau. Papa est près de lui. Parce que les pieds sont au sol, Estéban est calme. L'adulte arrose une plante. Le soir, maman ouvre aussi le balcon. Estéban se souvient. Il reste avec l'adulte. Il pose encore les pieds au sol. Il reste derrière la protection. Maman dit : oui. Pieds au sol, avec un adulte. Ils regardent le ciel. C'est doux.</t>
+          <t>Estéban est à la maison. Papa ouvre la porte du balcon. L'air sent le thym. Estéban reste avec l'adulte. On reste derrière la protection. Estéban pose les pieds au sol. Les pieds restent au sol. Il sent le bois sous les chaussettes. La protection est devant lui. Estéban pose les mains sur la protection. Il reste derrière la protection. Un oiseau chante. Papa, l'oiseau. Papa est près de lui. Parce que les pieds sont au sol, Estéban est calme. L'adulte arrose une plante. Le soir, maman ouvre aussi le balcon. Estéban se souvient. Il reste avec l'adulte. Il pose encore les pieds au sol. Il reste derrière la protection. Oui. Pieds au sol, avec un adulte. Ils regardent le ciel. C'est doux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Estéban est à la maison. Papa ouvre la porte du balcon. L'air sent le thym. Estéban reste avec l'adulte.
+papa|On reste derrière la protection.
+narrateur|Estéban pose les pieds au sol. Les pieds restent au sol. Il sent le bois sous les chaussettes. La protection est devant lui. Estéban pose les mains sur la protection. Il reste derrière la protection. Un oiseau chante.
+enfant-m|Papa, l'oiseau. Papa est près de lui. Parce que les pieds sont au sol, Estéban est calme. L'adulte arrose une plante.
+narrateur|Le soir, maman ouvre aussi le balcon. Estéban se souvient. Il reste avec l'adulte. Il pose encore les pieds au sol. Il reste derrière la protection.
+maman|Oui. Pieds au sol, avec un adulte.
+narrateur|Ils regardent le ciel. C'est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Estéban est au balcon. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1673,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Estéban a les pieds au sol. Il est derrière la protection. Papa puis maman, l'adulte, étaient là. Il a repris le geste le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1844,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Estéban et maman rentrent. Les pieds restent au sol.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2011,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2051,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.003-02.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Ils regardent le ciel. C'est doux.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1513,7 @@
           <t>narrateur|Estéban est au balcon. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1678,6 +1689,7 @@
           <t>narrateur|Estéban a les pieds au sol. Il est derrière la protection. Papa puis maman, l'adulte, étaient là. Il a repris le geste le soir.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1849,6 +1861,7 @@
           <t>narrateur|Estéban et maman rentrent. Les pieds restent au sol.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2016,6 +2029,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2034,7 +2048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2058,6 +2072,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2259,6 +2287,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.MAI.003-02.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Estéban au balcon deux fois</t>
+          <t>Le thym de Raphaël</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un pot de thym chauffe au soleil. Raphaël va au balcon avec papa. Le soir, maman ouvre encore. Il se souvient : pieds au sol, derrière la protection.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Estéban est à la maison. Papa ouvre la porte du balcon. L'air sent le thym. Estéban reste avec l'adulte. On reste derrière la protection. Estéban pose les pieds au sol. Les pieds restent au sol. Il sent le bois sous les chaussettes. La protection est devant lui. Estéban pose les mains sur la protection. Il reste derrière la protection. Un oiseau chante. Papa, l'oiseau. Papa est près de lui. Parce que les pieds sont au sol, Estéban est calme. L'adulte arrose une plante. Le soir, maman ouvre aussi le balcon. Estéban se souvient. Il reste avec l'adulte. Il pose encore les pieds au sol. Il reste derrière la protection. Oui. Pieds au sol, avec un adulte. Ils regardent le ciel. C'est doux.</t>
+          <t>Un pot de thym chauffe au soleil. Les petites feuilles sont grises et vertes. Ça sent le jardin, tout fort. La terre cuite est chaude sous le doigt. Un rayon glisse sur les dalles du balcon. Elles sont claires, un peu rèches. Une abeille butine, tout loin. Tu as senti le thym, Raphaël ? Oui, papa. Ça pique un peu le nez. Il a poussé, ce pot. En ce moment, papa ouvre la porte. L'air sent le thym, plus près. Raphaël reste avec l'adulte. On reste derrière la protection. D'accord, papa. Raphaël pose les pieds au sol. Les pieds restent au sol. Il sent le bois sous les chaussettes. La protection est devant lui. Raphaël pose les mains sur la protection. Il reste derrière la protection. Bravo. Tes pieds sont au sol. Un oiseau chante, tout près. Papa, l'oiseau. Je l'entends. On le regarde ici, avec moi. Papa est près de lui. Parce que les pieds sont au sol, Raphaël est calme. L'adulte arrose une plante. L'eau fait un petit bruit. Tu as fini de regarder l'oiseau ? Oui. Il est parti. On rentre un peu. Tu as fait du bon travail. Le soir, la lumière est plus douce. Maman ouvre aussi le balcon. Raphaël se souvient. Il reste avec l'adulte. Il pose encore les pieds au sol. Il reste derrière la protection. Oui. Pieds au sol, avec un adulte. Derrière la protection. Bravo, Raphaël. Tu t'es souvenu. Ils regardent le ciel. C'est doux. Tu vois l'étoile, là ? Oui, maman. On la regarde ici. Avec moi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,65 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Estéban est à la maison. Papa ouvre la porte du balcon. L'air sent le thym. Estéban reste avec l'adulte.
+          <t>narrateur|Un pot de thym chauffe au soleil.
+narrateur|Les petites feuilles sont grises et vertes.
+narrateur|Ça sent le jardin, tout fort.
+narrateur|La terre cuite est chaude sous le doigt.
+narrateur|Un rayon glisse sur les dalles du balcon.
+narrateur|Elles sont claires, un peu rèches.
+narrateur|Une abeille butine, tout loin.
+papa|Tu as senti le thym, Raphaël ?
+enfant-m|Oui, papa.
+enfant-m|Ça pique un peu le nez.
+maman|Il a poussé, ce pot.
+narrateur|En ce moment, papa ouvre la porte.
+narrateur|L'air sent le thym, plus près.
+narrateur|Raphaël reste avec l'adulte.
 papa|On reste derrière la protection.
-narrateur|Estéban pose les pieds au sol. Les pieds restent au sol. Il sent le bois sous les chaussettes. La protection est devant lui. Estéban pose les mains sur la protection. Il reste derrière la protection. Un oiseau chante.
-enfant-m|Papa, l'oiseau. Papa est près de lui. Parce que les pieds sont au sol, Estéban est calme. L'adulte arrose une plante.
-narrateur|Le soir, maman ouvre aussi le balcon. Estéban se souvient. Il reste avec l'adulte. Il pose encore les pieds au sol. Il reste derrière la protection.
-maman|Oui. Pieds au sol, avec un adulte.
-narrateur|Ils regardent le ciel. C'est doux.</t>
+enfant-m|D'accord, papa.
+narrateur|Raphaël pose les pieds au sol.
+narrateur|Les pieds restent au sol.
+narrateur|Il sent le bois sous les chaussettes.
+narrateur|La protection est devant lui.
+narrateur|Raphaël pose les mains sur la protection.
+narrateur|Il reste derrière la protection.
+papa|Bravo.
+papa|Tes pieds sont au sol.
+narrateur|Un oiseau chante, tout près.
+enfant-m|Papa, l'oiseau.
+papa|Je l'entends.
+papa|On le regarde ici, avec moi.
+narrateur|Papa est près de lui.
+narrateur|Parce que les pieds sont au sol, Raphaël est calme.
+narrateur|L'adulte arrose une plante.
+narrateur|L'eau fait un petit bruit.
+papa|Tu as fini de regarder l'oiseau ?
+enfant-m|Oui.
+enfant-m|Il est parti.
+papa|On rentre un peu.
+papa|Tu as fait du bon travail.
+narrateur|Le soir, la lumière est plus douce.
+narrateur|Maman ouvre aussi le balcon.
+narrateur|Raphaël se souvient.
+narrateur|Il reste avec l'adulte.
+narrateur|Il pose encore les pieds au sol.
+narrateur|Il reste derrière la protection.
+maman|Oui.
+maman|Pieds au sol, avec un adulte.
+enfant-m|Derrière la protection.
+maman|Bravo, Raphaël.
+maman|Tu t'es souvenu.
+narrateur|Ils regardent le ciel.
+narrateur|C'est doux.
+maman|Tu vois l'étoile, là ?
+enfant-m|Oui, maman.
+maman|On la regarde ici.
+maman|Avec moi.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>oiseau,eau</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1409,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Estéban est au balcon. Que fait-il ?</t>
+          <t>Raphaël est au balcon. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1510,7 +1569,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Estéban est au balcon. Que fait-il ?</t>
+          <t>narrateur|Raphaël est au balcon.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1538,7 +1598,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Estéban a les pieds au sol. Il est derrière la protection. Papa puis maman, l'adulte, étaient là. Il a repris le geste le soir.</t>
+          <t>Raphaël a les pieds au sol. Il est derrière la protection. Papa puis maman, l'adulte, étaient là. Il a repris le geste le soir. Tu t'es souvenu. Bravo, Raphaël. Pieds au sol. Avec l'adulte. Oui. C'est du bon travail. Tu restes derrière la protection ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1686,7 +1746,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Estéban a les pieds au sol. Il est derrière la protection. Papa puis maman, l'adulte, étaient là. Il a repris le geste le soir.</t>
+          <t>narrateur|Raphaël a les pieds au sol.
+narrateur|Il est derrière la protection.
+narrateur|Papa puis maman, l'adulte, étaient là.
+narrateur|Il a repris le geste le soir.
+papa|Tu t'es souvenu.
+maman|Bravo, Raphaël.
+enfant-m|Pieds au sol.
+enfant-m|Avec l'adulte.
+maman|Oui.
+maman|C'est du bon travail.
+papa|Tu restes derrière la protection ?
+enfant-m|Oui, papa.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1714,7 +1785,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Estéban et maman rentrent. Les pieds restent au sol.</t>
+          <t>Raphaël et maman rentrent. Les pieds restent au sol. Le thym sent encore, tout doux. On ferme la porte ? Oui, maman. Tu as les pieds au sol, jusqu'ici. Bravo. J'ai regardé l'étoile. Avec l'adulte. Derrière la protection. Tu veux t'asseoir un peu ? Oui. La chaise est près de la table. Tu t'es souvenu, le soir.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1858,7 +1929,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Estéban et maman rentrent. Les pieds restent au sol.</t>
+          <t>narrateur|Raphaël et maman rentrent.
+narrateur|Les pieds restent au sol.
+narrateur|Le thym sent encore, tout doux.
+maman|On ferme la porte ?
+enfant-m|Oui, maman.
+papa|Tu as les pieds au sol, jusqu'ici.
+papa|Bravo.
+enfant-m|J'ai regardé l'étoile.
+maman|Avec l'adulte.
+maman|Derrière la protection.
+maman|Tu veux t'asseoir un peu ?
+enfant-m|Oui.
+narrateur|La chaise est près de la table.
+papa|Tu t'es souvenu, le soir.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1886,7 +1970,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le matin, avec papa. Le soir, avec maman. Pieds au sol. Bravo. Tu as fait du bon travail. Le pot de thym reste au chaud. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2026,7 +2110,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|Le matin, avec papa.
+enfant-m|Le soir, avec maman.
+papa|Pieds au sol.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le pot de thym reste au chaud.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2048,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2086,6 +2176,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.003-02.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un pot de thym chauffe au soleil. Les petites feuilles sont grises et vertes. Ça sent le jardin, tout fort. La terre cuite est chaude sous le doigt. Un rayon glisse sur les dalles du balcon. Elles sont claires, un peu rèches. Une abeille butine, tout loin. Tu as senti le thym, Raphaël ? Oui, papa. Ça pique un peu le nez. Il a poussé, ce pot. En ce moment, papa ouvre la porte. L'air sent le thym, plus près. Raphaël reste avec l'adulte. On reste derrière la protection. D'accord, papa. Raphaël pose les pieds au sol. Les pieds restent au sol. Il sent le bois sous les chaussettes. La protection est devant lui. Raphaël pose les mains sur la protection. Il reste derrière la protection. Bravo. Tes pieds sont au sol. Un oiseau chante, tout près. Papa, l'oiseau. Je l'entends. On le regarde ici, avec moi. Papa est près de lui. Parce que les pieds sont au sol, Raphaël est calme. L'adulte arrose une plante. L'eau fait un petit bruit. Tu as fini de regarder l'oiseau ? Oui. Il est parti. On rentre un peu. Tu as fait du bon travail. Le soir, la lumière est plus douce. Maman ouvre aussi le balcon. Raphaël se souvient. Il reste avec l'adulte. Il pose encore les pieds au sol. Il reste derrière la protection. Oui. Pieds au sol, avec un adulte. Derrière la protection. Bravo, Raphaël. Tu t'es souvenu. Ils regardent le ciel. C'est doux. Tu vois l'étoile, là ? Oui, maman. On la regarde ici. Avec moi.</t>
+          <t>Un pot de thym chauffe au soleil. Les petites feuilles sont grises et vertes. Ça sent le jardin, tout fort. La terre cuite est chaude sous le doigt. Un rayon glisse sur les dalles du balcon. Elles sont claires, un peu rèches. Une abeille butine, tout loin. Tu as senti le thym, Raphaël ? Oui, papa. Ça pique un peu le nez. Il a poussé, ce pot. En ce moment, papa ouvre la porte. L'air sent le thym, plus près. Raphaël reste avec l'adulte. On reste derrière la protection. D'accord, papa. Raphaël pose les pieds au sol. Les pieds restent au sol. Il sent le bois sous les chaussettes. La protection est devant lui. Raphaël pose les mains sur la protection. Il reste derrière la protection. Bravo. Tes pieds sont au sol. Un oiseau chante, tout près. Papa, l'oiseau. Je l'entends. On le regarde ici, avec moi. Papa est près de lui. Parce que les pieds sont au sol, Raphaël est calme. L'adulte arrose une plante. L'eau fait un petit bruit. Tu as fini de regarder l'oiseau ? Oui. Il est parti. On rentre un peu. Le soir, la lumière est plus douce. Maman ouvre aussi le balcon. Raphaël se souvient. Il reste avec l'adulte. Il pose encore les pieds au sol. Il reste derrière la protection. Oui. Pieds au sol, avec un adulte. Derrière la protection. Bravo, Raphaël. Tu t'es souvenu. Ils regardent le ciel. C'est doux. Tu vois l'étoile, là ? Oui, maman. On la regarde ici. Avec moi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Estéban est à la maison. Papa ouvre la porte du balcon. L'air sent le thym. Estéban reste avec l'adulte. Papa dit : on reste derrière la protection. Estéban pose les &lt;emphasis level="moderate"&gt;pieds&lt;/emphasis&gt; au sol. Les pieds restent au sol. Il sent le bois sous les chaussettes. La protection est devant lui. Estéban pose les mains sur la protection. Il reste derrière la protection. Un oiseau chante. Estéban dit : papa, l'oiseau. Papa est près de lui. Parce que les pieds sont au sol, Estéban est calme. L'adulte arrose une plante. Le soir, maman ouvre aussi le balcon. Estéban se souvient. Il reste avec l'adulte. Il pose encore les pieds au sol. Il reste derrière la protection. Maman dit : oui. Pieds au sol, avec un adulte. Ils regardent le ciel. C'est doux.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un pot de thym chauffe au soleil. Les petites feuilles sont grises et vertes. Ça sent le jardin, tout fort. La terre cuite est chaude sous le doigt. Un rayon glisse sur les dalles du balcon. Elles sont claires, un peu rèches. Une abeille butine, tout loin. Tu as senti le thym, Raphaël ? Oui, papa. Ça pique un peu le nez. Il a poussé, ce pot. En ce moment, papa ouvre la porte. L'air sent le thym, plus près. Raphaël reste avec l'adulte. On reste derrière la protection. D'accord, papa. Raphaël pose les pieds au sol. Les pieds restent au sol. Il sent le bois sous les chaussettes. La protection est devant lui. Raphaël pose les mains sur la protection. Il reste derrière la protection. Bravo. Tes pieds sont au sol. Un oiseau chante, tout près. Papa, l'oiseau. Je l'entends. On le regarde ici, avec moi. Papa est près de lui. Parce que les pieds sont au sol, Raphaël est calme. L'adulte arrose une plante. L'eau fait un petit bruit. Tu as fini de regarder l'oiseau ? Oui. Il est parti. On rentre un peu. Le soir, la lumière est plus douce. Maman ouvre aussi le balcon. Raphaël se souvient. Il reste avec l'adulte. Il pose encore les pieds au sol. Il reste derrière la protection. Oui. Pieds au sol, avec un adulte. Derrière la protection. Bravo, Raphaël. Tu t'es souvenu. Ils regardent le ciel. C'est doux. Tu vois l'étoile, là ? Oui, maman. On la regarde ici. Avec moi.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1360,7 +1360,6 @@
 enfant-m|Oui.
 enfant-m|Il est parti.
 papa|On rentre un peu.
-papa|Tu as fait du bon travail.
 narrateur|Le soir, la lumière est plus douce.
 narrateur|Maman ouvre aussi le balcon.
 narrateur|Raphaël se souvient.
@@ -1414,7 +1413,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Estéban est au balcon. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël est au balcon. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1573,7 +1572,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1598,12 +1596,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a les pieds au sol. Il est derrière la protection. Papa puis maman, l'adulte, étaient là. Il a repris le geste le soir. Tu t'es souvenu. Bravo, Raphaël. Pieds au sol. Avec l'adulte. Oui. C'est du bon travail. Tu restes derrière la protection ? Oui, papa.</t>
+          <t>Raphaël a les pieds au sol. Il est derrière la protection. Papa puis maman, l'adulte, étaient là. Il a repris le geste le soir. Tu t'es souvenu. Bravo, Raphaël. Pieds au sol. Avec l'adulte. Oui. Tu restes derrière la protection ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Estéban a les &lt;emphasis level="moderate"&gt;pieds&lt;/emphasis&gt; au sol. Il est derrière la protection. Papa puis maman, l'adulte, étaient là. Il a repris le geste le soir.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a les pieds au sol. Il est derrière la protection. Papa puis maman, l'adulte, étaient là. Il a repris le geste le soir. Tu t'es souvenu. Bravo, Raphaël. Pieds au sol. Avec l'adulte. Oui. Tu restes derrière la protection ? Oui, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1755,12 +1753,10 @@
 enfant-m|Pieds au sol.
 enfant-m|Avec l'adulte.
 maman|Oui.
-maman|C'est du bon travail.
 papa|Tu restes derrière la protection ?
 enfant-m|Oui, papa.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1790,7 +1786,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Estéban et maman rentrent. Les &lt;emphasis level="moderate"&gt;pieds&lt;/emphasis&gt; restent au sol.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël et maman rentrent. Les pieds restent au sol. Le thym sent encore, tout doux. On ferme la porte ? Oui, maman. Tu as les pieds au sol, jusqu'ici. Bravo. J'ai regardé l'étoile. Avec l'adulte. Derrière la protection. Tu veux t'asseoir un peu ? Oui. La chaise est près de la table. Tu t'es souvenu, le soir.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1945,7 +1941,6 @@
 papa|Tu t'es souvenu, le soir.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1970,12 +1965,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le matin, avec papa. Le soir, avec maman. Pieds au sol. Bravo. Tu as fait du bon travail. Le pot de thym reste au chaud. L'histoire est finie.</t>
+          <t>Le matin, avec papa. Le soir, avec maman. Pieds au sol. Bravo. Le pot de thym reste au chaud.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le matin, avec papa. Le soir, avec maman. Pieds au sol. Bravo. Le pot de thym reste au chaud.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2114,12 +2109,9 @@
 enfant-m|Le soir, avec maman.
 papa|Pieds au sol.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le pot de thym reste au chaud.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le pot de thym reste au chaud.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2138,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2183,6 +2175,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.003-02.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-02.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Estéban, papa, maman</t>
+          <t>Raphaël, papa, maman</t>
         </is>
       </c>
     </row>
